--- a/data_dummy.xlsx
+++ b/data_dummy.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Hello World\EOQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Python\EOQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9917941-9DF3-425B-A54B-A30EE7136A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E16925-30D0-4808-9695-D74BA7D51933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E10174BD-42BE-49AC-BBC5-1602FCBAD37D}"/>
   </bookViews>
@@ -455,15 +455,15 @@
   <dimension ref="A2:I272"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
